--- a/artfynd/A 1688-2022 artfynd.xlsx
+++ b/artfynd/A 1688-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1688-2022 artfynd.xlsx
+++ b/artfynd/A 1688-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1290,7 +1290,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102670772</v>
+        <v>102670537</v>
       </c>
       <c r="B7" t="n">
         <v>96334</v>
@@ -1325,26 +1325,26 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Avesta, Dlr</t>
+          <t>Folkärna Granliden, Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569677.8683713591</v>
+        <v>569725.1174450946</v>
       </c>
       <c r="R7" t="n">
-        <v>6675592.421863126</v>
+        <v>6675621.659906693</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,7 +1413,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102670537</v>
+        <v>102670960</v>
       </c>
       <c r="B8" t="n">
         <v>96334</v>
@@ -1451,23 +1451,22 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Folkärna Granliden, Avesta, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569725.1174450946</v>
+        <v>569665.4611745073</v>
       </c>
       <c r="R8" t="n">
-        <v>6675621.659906693</v>
+        <v>6675590.196939202</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1499,7 +1498,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1509,7 +1508,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,19 +1523,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t xml:space="preserve">Anette  Lyck </t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t xml:space="preserve">Anette  Lyck </t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102670960</v>
+        <v>102671520</v>
       </c>
       <c r="B9" t="n">
         <v>96334</v>
@@ -1571,25 +1570,26 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Avesta, Dlr</t>
+          <t>Folkärna Granliden, Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569665.4611745073</v>
+        <v>569558.5844526507</v>
       </c>
       <c r="R9" t="n">
-        <v>6675590.196939202</v>
+        <v>6675501.657071872</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,19 +1646,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anette  Lyck </t>
+          <t xml:space="preserve">FREDRIK  Månsson </t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anette  Lyck </t>
+          <t xml:space="preserve">FREDRIK  Månsson </t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102671520</v>
+        <v>102671253</v>
       </c>
       <c r="B10" t="n">
         <v>96334</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1705,14 +1705,14 @@
       <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Folkärna Granliden, Avesta, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569558.5844526507</v>
+        <v>569592.1016652404</v>
       </c>
       <c r="R10" t="n">
-        <v>6675501.657071872</v>
+        <v>6675546.044993746</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1781,10 +1781,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102671253</v>
+        <v>102671336</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
+        <v>56411</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1793,49 +1793,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569592.1016652404</v>
+        <v>569562.5450179246</v>
       </c>
       <c r="R11" t="n">
-        <v>6675546.044993746</v>
+        <v>6675529.076482357</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1867,7 +1863,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1877,7 +1873,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1904,10 +1900,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102671336</v>
+        <v>102671987</v>
       </c>
       <c r="B12" t="n">
-        <v>56411</v>
+        <v>96334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1916,45 +1912,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Avesta, Dlr</t>
+          <t>Folkärna Granliden, Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569562.5450179246</v>
+        <v>569804.1251018697</v>
       </c>
       <c r="R12" t="n">
-        <v>6675529.076482357</v>
+        <v>6675630.623943884</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,7 +2023,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102671987</v>
+        <v>102671474</v>
       </c>
       <c r="B13" t="n">
         <v>96334</v>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569804.1251018697</v>
+        <v>569562.9324783079</v>
       </c>
       <c r="R13" t="n">
-        <v>6675630.623943884</v>
+        <v>6675508.700083724</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2146,7 +2146,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102671474</v>
+        <v>102671206</v>
       </c>
       <c r="B14" t="n">
         <v>96334</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2193,14 +2193,14 @@
       <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Folkärna Granliden, Avesta, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569562.9324783079</v>
+        <v>569600.9676612311</v>
       </c>
       <c r="R14" t="n">
-        <v>6675508.700083724</v>
+        <v>6675551.185277863</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2269,7 +2269,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102671206</v>
+        <v>102670465</v>
       </c>
       <c r="B15" t="n">
         <v>96334</v>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2316,14 +2316,14 @@
       <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Avesta, Dlr</t>
+          <t>Folkärna Granliden, Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569600.9676612311</v>
+        <v>569727.9053055532</v>
       </c>
       <c r="R15" t="n">
-        <v>6675551.185277863</v>
+        <v>6675632.15322452</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2392,7 +2392,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102670465</v>
+        <v>102671284</v>
       </c>
       <c r="B16" t="n">
         <v>96334</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2439,14 +2439,14 @@
       <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Folkärna Granliden, Avesta, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569727.9053055532</v>
+        <v>569584.8771084807</v>
       </c>
       <c r="R16" t="n">
-        <v>6675632.15322452</v>
+        <v>6675559.330901646</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2515,7 +2515,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102671284</v>
+        <v>102671266</v>
       </c>
       <c r="B17" t="n">
         <v>96334</v>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569584.8771084807</v>
+        <v>569590.1009777011</v>
       </c>
       <c r="R17" t="n">
-        <v>6675559.330901646</v>
+        <v>6675546.504095966</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2638,7 +2638,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102671266</v>
+        <v>102671090</v>
       </c>
       <c r="B18" t="n">
         <v>96334</v>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569590.1009777011</v>
+        <v>569609.773492854</v>
       </c>
       <c r="R18" t="n">
-        <v>6675546.504095966</v>
+        <v>6675585.656770015</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2761,7 +2761,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102671090</v>
+        <v>102671966</v>
       </c>
       <c r="B19" t="n">
         <v>96334</v>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2808,14 +2808,14 @@
       <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Avesta, Dlr</t>
+          <t>Folkärna Granliden, Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569609.773492854</v>
+        <v>569803.1105417433</v>
       </c>
       <c r="R19" t="n">
-        <v>6675585.656770015</v>
+        <v>6675631.598886861</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2884,7 +2884,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102671966</v>
+        <v>102671827</v>
       </c>
       <c r="B20" t="n">
         <v>96334</v>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2935,10 +2935,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569803.1105417433</v>
+        <v>569669.30363445</v>
       </c>
       <c r="R20" t="n">
-        <v>6675631.598886861</v>
+        <v>6675519.176118471</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3007,7 +3007,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102671827</v>
+        <v>102671542</v>
       </c>
       <c r="B21" t="n">
         <v>96334</v>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569669.30363445</v>
+        <v>569536.3499844668</v>
       </c>
       <c r="R21" t="n">
-        <v>6675519.176118471</v>
+        <v>6675518.635188427</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3130,7 +3130,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102671542</v>
+        <v>102671303</v>
       </c>
       <c r="B22" t="n">
         <v>96334</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3177,14 +3177,14 @@
       <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Folkärna Granliden, Avesta, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569536.3499844668</v>
+        <v>569578.4182444878</v>
       </c>
       <c r="R22" t="n">
-        <v>6675518.635188427</v>
+        <v>6675532.361329971</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3250,129 +3250,6 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>102671303</v>
-      </c>
-      <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Avesta, Dlr</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>569578.4182444878</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6675532.361329971</v>
-      </c>
-      <c r="S23" t="n">
-        <v>25</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Avesta</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Folkärna</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1688-2022 artfynd.xlsx
+++ b/artfynd/A 1688-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102670432</v>
+        <v>102671336</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Folkärna Granliden, Avesta, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569735.7804681303</v>
+        <v>569563</v>
       </c>
       <c r="R2" t="n">
-        <v>6675663.126557668</v>
+        <v>6675529</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +762,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,27 +777,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102670996</v>
+        <v>102670416</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,14 +831,14 @@
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Avesta, Dlr</t>
+          <t>Folkärna Granliden, Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569676.8727670654</v>
+        <v>569750</v>
       </c>
       <c r="R3" t="n">
-        <v>6675592.402899855</v>
+        <v>6675696</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,27 +895,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102671711</v>
+        <v>102670432</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -972,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569572.8446092209</v>
+        <v>569735</v>
       </c>
       <c r="R4" t="n">
-        <v>6675485.024510855</v>
+        <v>6675663</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1007,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,27 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102671236</v>
+        <v>102670465</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1091,14 +1067,14 @@
       <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Avesta, Dlr</t>
+          <t>Folkärna Granliden, Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569602.9588919941</v>
+        <v>569728</v>
       </c>
       <c r="R5" t="n">
-        <v>6675551.223163219</v>
+        <v>6675632</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1130,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,27 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102671853</v>
+        <v>102670537</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1173,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1218,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569674.7038437949</v>
+        <v>569725</v>
       </c>
       <c r="R6" t="n">
-        <v>6675523.256288636</v>
+        <v>6675622</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1253,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1263,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,27 +1249,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102670537</v>
+        <v>102670772</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,26 +1291,26 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Folkärna Granliden, Avesta, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569725.1174450946</v>
+        <v>569677</v>
       </c>
       <c r="R7" t="n">
-        <v>6675621.659906693</v>
+        <v>6675592</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1376,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,27 +1367,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102670960</v>
+        <v>102670902</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1409,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1463,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569665.4611745073</v>
+        <v>569665</v>
       </c>
       <c r="R8" t="n">
-        <v>6675590.196939202</v>
+        <v>6675590</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1498,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1508,7 +1474,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,27 +1489,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anette  Lyck </t>
+          <t>Anette  Lyck</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anette  Lyck </t>
+          <t>Anette  Lyck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102671520</v>
+        <v>102671090</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1531,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1582,14 +1543,14 @@
       <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Folkärna Granliden, Avesta, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569558.5844526507</v>
+        <v>569610</v>
       </c>
       <c r="R9" t="n">
-        <v>6675501.657071872</v>
+        <v>6675585</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1621,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1631,7 +1592,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,27 +1607,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102671253</v>
+        <v>102671206</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1649,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1709,10 +1665,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569592.1016652404</v>
+        <v>569601</v>
       </c>
       <c r="R10" t="n">
-        <v>6675546.044993746</v>
+        <v>6675551</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1744,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1754,7 +1710,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,69 +1725,68 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102671336</v>
+        <v>102671236</v>
       </c>
       <c r="B11" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569562.5450179246</v>
+        <v>569603</v>
       </c>
       <c r="R11" t="n">
-        <v>6675529.076482357</v>
+        <v>6675551</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1863,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,7 +1828,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1888,27 +1843,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102671987</v>
+        <v>102671253</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1885,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1947,14 +1897,14 @@
       <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Folkärna Granliden, Avesta, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569804.1251018697</v>
+        <v>569592</v>
       </c>
       <c r="R12" t="n">
-        <v>6675630.623943884</v>
+        <v>6675546</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1986,7 +1936,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1996,7 +1946,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2011,27 +1961,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102671474</v>
+        <v>102671266</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2058,7 +2003,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2070,14 +2015,14 @@
       <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Folkärna Granliden, Avesta, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569562.9324783079</v>
+        <v>569591</v>
       </c>
       <c r="R13" t="n">
-        <v>6675508.700083724</v>
+        <v>6675546</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2109,7 +2054,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2119,7 +2064,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,27 +2079,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102671206</v>
+        <v>102671284</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,7 +2121,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2197,10 +2137,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569600.9676612311</v>
+        <v>569585</v>
       </c>
       <c r="R14" t="n">
-        <v>6675551.185277863</v>
+        <v>6675559</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2232,7 +2172,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2242,7 +2182,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2257,27 +2197,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102670465</v>
+        <v>102671303</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2304,7 +2239,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2316,14 +2251,14 @@
       <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Folkärna Granliden, Avesta, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569727.9053055532</v>
+        <v>569578</v>
       </c>
       <c r="R15" t="n">
-        <v>6675632.15322452</v>
+        <v>6675532</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2355,7 +2290,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2365,7 +2300,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2380,27 +2315,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102671284</v>
+        <v>102671474</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2357,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2439,14 +2369,14 @@
       <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Avesta, Dlr</t>
+          <t>Folkärna Granliden, Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569584.8771084807</v>
+        <v>569563</v>
       </c>
       <c r="R16" t="n">
-        <v>6675559.330901646</v>
+        <v>6675509</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2478,7 +2408,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2488,7 +2418,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2503,27 +2433,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102671266</v>
+        <v>102671520</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2550,7 +2475,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2562,14 +2487,14 @@
       <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Avesta, Dlr</t>
+          <t>Folkärna Granliden, Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569590.1009777011</v>
+        <v>569559</v>
       </c>
       <c r="R17" t="n">
-        <v>6675546.504095966</v>
+        <v>6675502</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2601,7 +2526,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2611,7 +2536,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2626,27 +2551,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102671090</v>
+        <v>102671542</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2673,7 +2593,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2685,14 +2605,14 @@
       <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Avesta, Dlr</t>
+          <t>Folkärna Granliden, Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569609.773492854</v>
+        <v>569537</v>
       </c>
       <c r="R18" t="n">
-        <v>6675585.656770015</v>
+        <v>6675518</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2724,7 +2644,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2734,7 +2654,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2749,27 +2669,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102671966</v>
+        <v>102671711</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2812,10 +2727,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569803.1105417433</v>
+        <v>569573</v>
       </c>
       <c r="R19" t="n">
-        <v>6675631.598886861</v>
+        <v>6675486</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2847,7 +2762,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2857,7 +2772,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2872,12 +2787,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2887,12 +2802,7 @@
         <v>102671827</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2935,10 +2845,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569669.30363445</v>
+        <v>569670</v>
       </c>
       <c r="R20" t="n">
-        <v>6675519.176118471</v>
+        <v>6675519</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2995,27 +2905,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102671542</v>
+        <v>102671853</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +2947,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3058,10 +2963,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569536.3499844668</v>
+        <v>569674</v>
       </c>
       <c r="R21" t="n">
-        <v>6675518.635188427</v>
+        <v>6675524</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3093,7 +2998,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3103,7 +3008,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3118,27 +3023,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102671303</v>
+        <v>102671966</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3165,7 +3065,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3177,14 +3077,14 @@
       <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Avesta, Dlr</t>
+          <t>Folkärna Granliden, Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569578.4182444878</v>
+        <v>569803</v>
       </c>
       <c r="R22" t="n">
-        <v>6675532.361329971</v>
+        <v>6675632</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3216,7 +3116,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3226,7 +3126,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3241,15 +3141,133 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>102671987</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Folkärna Granliden, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>569804</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6675631</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Folkärna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-08-04</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-08-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1688-2022 artfynd.xlsx
+++ b/artfynd/A 1688-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671336</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102670416</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102670432</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102670465</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1258,6 +1283,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102670537</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1376,6 +1406,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102670772</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1498,6 +1533,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102670902</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1616,6 +1656,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671090</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1734,6 +1779,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671206</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1852,6 +1902,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671236</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1970,6 +2025,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671253</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2088,6 +2148,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671266</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2206,6 +2271,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671284</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2324,6 +2394,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671303</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2442,6 +2517,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671474</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2560,6 +2640,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671520</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2678,6 +2763,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671542</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2796,6 +2886,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671711</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2914,6 +3009,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671827</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3032,6 +3132,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671853</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3150,6 +3255,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671966</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3268,8 +3378,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671987</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>